--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N12_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>20.34342206734527</v>
       </c>
       <c r="E2" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F2" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>2.85940437089933</v>
       </c>
       <c r="E3" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F3" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>21.6332361195124</v>
       </c>
       <c r="E4" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F4" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>21.92767455753377</v>
       </c>
       <c r="E5" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F5" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.1472345903501</v>
+        <v>20.01207706999979</v>
       </c>
       <c r="D6" t="n">
-        <v>2.121320343559642</v>
+        <v>9.797654939371881</v>
       </c>
       <c r="E6" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F6" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.2125803579615</v>
+        <v>22.1472345903501</v>
       </c>
       <c r="D7" t="n">
-        <v>10.69894423157134</v>
+        <v>2.121320343559642</v>
       </c>
       <c r="E7" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F7" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.624537298212898</v>
+        <v>28.2125803579615</v>
       </c>
       <c r="D8" t="n">
-        <v>24.71777555823002</v>
+        <v>10.69894423157134</v>
       </c>
       <c r="E8" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F8" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.852620177540735</v>
+        <v>28.26392480198494</v>
       </c>
       <c r="D9" t="n">
-        <v>2.339970445878092</v>
+        <v>17.48567594769422</v>
       </c>
       <c r="E9" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F9" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.620408411181817</v>
+        <v>9.624537298212898</v>
       </c>
       <c r="D10" t="n">
-        <v>5.0657775562503</v>
+        <v>24.71777555823002</v>
       </c>
       <c r="E10" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F10" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.5879486085963</v>
+        <v>5.852620177540735</v>
       </c>
       <c r="D11" t="n">
-        <v>6.41475652750668</v>
+        <v>2.339970445878092</v>
       </c>
       <c r="E11" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F11" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.51983003469053</v>
+        <v>8.620408411181817</v>
       </c>
       <c r="D12" t="n">
-        <v>18.51875925769447</v>
+        <v>5.0657775562503</v>
       </c>
       <c r="E12" t="n">
-        <v>10.35663593319276</v>
+        <v>9.798933041749137</v>
       </c>
       <c r="F12" t="n">
-        <v>8.260316857989331</v>
+        <v>7.796632288022227</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,23 +832,87 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
+        <v>12.5879486085963</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.41475652750668</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.798933041749137</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.796632288022227</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>T6588</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W0053F0001T0006Z000C1N12.png</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17.51983003469053</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18.51875925769447</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.798933041749137</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.796632288022227</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>T6588</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W0053F0001T0006Z000C1N12.png</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
         <v>20.08315660261282</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D15" t="n">
         <v>12.06109928911988</v>
       </c>
-      <c r="E13" t="n">
-        <v>10.35663593319276</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8.260316857989331</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>T6588</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E15" t="n">
+        <v>9.798933041749137</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.796632288022227</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T6588</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.11517099159721</v>
+        <v>6.356215286134547</v>
       </c>
       <c r="D2" t="n">
-        <v>20.34342206734527</v>
+        <v>3.305806085943606</v>
       </c>
       <c r="E2" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F2" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.52740410340776</v>
+        <v>2.685703166803761</v>
       </c>
       <c r="D3" t="n">
-        <v>2.85940437089933</v>
+        <v>0.4646532102711411</v>
       </c>
       <c r="E3" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F3" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.93208705988061</v>
+        <v>5.838964147230599</v>
       </c>
       <c r="D4" t="n">
-        <v>21.6332361195124</v>
+        <v>3.515400869420765</v>
       </c>
       <c r="E4" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F4" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.38129477047116</v>
+        <v>4.774460400201564</v>
       </c>
       <c r="D5" t="n">
-        <v>21.92767455753377</v>
+        <v>3.563247115599238</v>
       </c>
       <c r="E5" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F5" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.01207706999979</v>
+        <v>3.251962523874966</v>
       </c>
       <c r="D6" t="n">
-        <v>9.797654939371881</v>
+        <v>1.592118927647931</v>
       </c>
       <c r="E6" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F6" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.1472345903501</v>
+        <v>3.598925620931892</v>
       </c>
       <c r="D7" t="n">
-        <v>2.121320343559642</v>
+        <v>0.3447145558284419</v>
       </c>
       <c r="E7" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F7" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.2125803579615</v>
+        <v>4.584544308168744</v>
       </c>
       <c r="D8" t="n">
-        <v>10.69894423157134</v>
+        <v>1.738578437630343</v>
       </c>
       <c r="E8" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F8" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.26392480198494</v>
+        <v>4.592887780322553</v>
       </c>
       <c r="D9" t="n">
-        <v>17.48567594769422</v>
+        <v>2.841422341500311</v>
       </c>
       <c r="E9" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F9" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.624537298212898</v>
+        <v>1.563987310959596</v>
       </c>
       <c r="D10" t="n">
-        <v>24.71777555823002</v>
+        <v>4.016638528212378</v>
       </c>
       <c r="E10" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F10" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.852620177540735</v>
+        <v>0.9510507788503695</v>
       </c>
       <c r="D11" t="n">
-        <v>2.339970445878092</v>
+        <v>0.3802451974551899</v>
       </c>
       <c r="E11" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F11" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.620408411181817</v>
+        <v>1.400816366817045</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0657775562503</v>
+        <v>0.8231888528906738</v>
       </c>
       <c r="E12" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F12" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.5879486085963</v>
+        <v>2.045541648896899</v>
       </c>
       <c r="D13" t="n">
-        <v>6.41475652750668</v>
+        <v>1.042397935719835</v>
       </c>
       <c r="E13" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F13" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51983003469053</v>
+        <v>2.846972380637212</v>
       </c>
       <c r="D14" t="n">
-        <v>18.51875925769447</v>
+        <v>3.009298379375351</v>
       </c>
       <c r="E14" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F14" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.08315660261282</v>
+        <v>3.263512947924584</v>
       </c>
       <c r="D15" t="n">
-        <v>12.06109928911988</v>
+        <v>1.95992863448198</v>
       </c>
       <c r="E15" t="n">
-        <v>9.798933041749137</v>
+        <v>1.592326619284235</v>
       </c>
       <c r="F15" t="n">
-        <v>7.796632288022227</v>
+        <v>1.266952746803612</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
